--- a/data-manipulation-scripts/sheets-cleanup/sheets/EMBREAGEM PRIMÁRIA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/EMBREAGEM PRIMÁRIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -52,13 +52,19 @@
     <t>7899468065736</t>
   </si>
   <si>
-    <t>TRANSMISSAO PRIMARIA COMPLETA TRILHA PCX150 2014 A 2015</t>
+    <t>EMBREAGEM PRIMARIA COMPLETA TRILHA PCX150 2014 A 2015</t>
   </si>
   <si>
     <t>7899468087905</t>
   </si>
   <si>
-    <t>TRANSMISSAO PRIMARIA COMPLETA MHX NEO125 2017 A 2023</t>
+    <t>EMBREAGEM PRIMARIA COMPLETA MHX NEO125 2017 A 2023</t>
+  </si>
+  <si>
+    <t>7899468090431</t>
+  </si>
+  <si>
+    <t>EMBREAGEM PRIMARIA COMPLETA MHX NMAX160 2017 A 2020</t>
   </si>
 </sst>
 </file>
@@ -527,7 +533,7 @@
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="7">
@@ -563,13 +569,15 @@
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7">
         <v>1.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="4">
+        <v>380.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -594,10 +602,38 @@
       <c r="Z7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
     </row>
     <row r="9">
       <c r="A9" s="8"/>
